--- a/artfynd/A 54734-2022 artfynd.xlsx
+++ b/artfynd/A 54734-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54734-2022 artfynd.xlsx
+++ b/artfynd/A 54734-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY73"/>
+  <dimension ref="A1:AY85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>67152879</v>
+        <v>67152869</v>
       </c>
       <c r="B2" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540320.8363758735</v>
+        <v>540102</v>
       </c>
       <c r="R2" t="n">
-        <v>7226423.608728886</v>
+        <v>7226451</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +775,7 @@
         <v>67152864</v>
       </c>
       <c r="B3" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540135.9176101362</v>
+        <v>540136</v>
       </c>
       <c r="R3" t="n">
-        <v>7226457.270392062</v>
+        <v>7226457</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +840,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>67153012</v>
+        <v>67199645</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540575.3409803826</v>
+        <v>540087</v>
       </c>
       <c r="R4" t="n">
-        <v>7226506.167879461</v>
+        <v>7226499</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,19 +937,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>67153007</v>
+        <v>67152976</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,39 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Västansjön S sidan, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540027.8181282112</v>
+        <v>540581</v>
       </c>
       <c r="R5" t="n">
-        <v>7226509.647816988</v>
+        <v>7226474</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1089,19 +1034,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,22 +1056,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
+          <t>Anton Gustafsson, Eino Kenttä, Johanna Eriksson, Ingemar Södergren, Linda Johannesson, Nils Ericson, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>67153021</v>
+        <v>67152977</v>
       </c>
       <c r="B6" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540174.4456780271</v>
+        <v>540575</v>
       </c>
       <c r="R6" t="n">
-        <v>7226442.229412019</v>
+        <v>7226504</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1201,19 +1131,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,44 +1153,39 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
+          <t>Anton Gustafsson, Eino Kenttä, Johanna Eriksson, Ingemar Södergren, Linda Johannesson, Nils Ericson, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>67152999</v>
+        <v>67152978</v>
       </c>
       <c r="B7" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540109.4646777015</v>
+        <v>540558</v>
       </c>
       <c r="R7" t="n">
-        <v>7226451.443404212</v>
+        <v>7226512</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1313,19 +1228,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,22 +1250,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
+          <t>Anton Gustafsson, Eino Kenttä, Johanna Eriksson, Ingemar Södergren, Linda Johannesson, Nils Ericson, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>67152872</v>
+        <v>67152979</v>
       </c>
       <c r="B8" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540512.2407278703</v>
+        <v>539968</v>
       </c>
       <c r="R8" t="n">
-        <v>7226531.803317063</v>
+        <v>7226613</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1425,19 +1325,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,22 +1347,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
+          <t>Anton Gustafsson, Eino Kenttä, Johanna Eriksson, Ingemar Södergren, Linda Johannesson, Nils Ericson, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>67152881</v>
+        <v>67904694</v>
       </c>
       <c r="B9" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,34 +1365,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Västansjön S sidan, Ås lm</t>
+          <t>Västansjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540088.2741789528</v>
+        <v>539871</v>
       </c>
       <c r="R9" t="n">
-        <v>7226492.378885672</v>
+        <v>7226610</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,22 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,22 +1444,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
+          <t>Isak Vahlström, Elias Forsberg, Billy Lindblom</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>67152874</v>
+        <v>67152929</v>
       </c>
       <c r="B10" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540184.6312169316</v>
+        <v>540514</v>
       </c>
       <c r="R10" t="n">
-        <v>7226436.478687976</v>
+        <v>7226533</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1649,19 +1519,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>67152934</v>
+        <v>67152930</v>
       </c>
       <c r="B11" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540162.8073189018</v>
+        <v>540471</v>
       </c>
       <c r="R11" t="n">
-        <v>7226492.968856091</v>
+        <v>7226541</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1761,19 +1616,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,15 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>67152990</v>
+        <v>67152934</v>
       </c>
       <c r="B12" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1816,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1840,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540111.4730948005</v>
+        <v>540163</v>
       </c>
       <c r="R12" t="n">
-        <v>7226458.621529009</v>
+        <v>7226493</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1873,19 +1713,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>67152976</v>
+        <v>67199606</v>
       </c>
       <c r="B13" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1928,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>864</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1952,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540580.837733451</v>
+        <v>540578</v>
       </c>
       <c r="R13" t="n">
-        <v>7226473.854094513</v>
+        <v>7226571</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1985,19 +1810,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,15 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>67152904</v>
+        <v>67904770</v>
       </c>
       <c r="B14" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2040,34 +1850,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Västansjön S sidan, Ås lm</t>
+          <t>Västansjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540562.715027562</v>
+        <v>540393</v>
       </c>
       <c r="R14" t="n">
-        <v>7226505.574153036</v>
+        <v>7226300</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2094,22 +1904,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2129,44 +1929,39 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
+          <t>Isak Vahlström, Elias Forsberg, Billy Lindblom</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>67153022</v>
+        <v>67199636</v>
       </c>
       <c r="B15" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92721</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>918</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2176,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540164.0876194227</v>
+        <v>540042</v>
       </c>
       <c r="R15" t="n">
-        <v>7226491.724323416</v>
+        <v>7226730</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2209,19 +2004,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2248,15 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>67152978</v>
+        <v>67152904</v>
       </c>
       <c r="B16" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2264,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2288,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540557.575882217</v>
+        <v>540563</v>
       </c>
       <c r="R16" t="n">
-        <v>7226511.81325049</v>
+        <v>7226506</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2321,19 +2101,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2360,37 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>67152866</v>
+        <v>67152905</v>
       </c>
       <c r="B17" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2400,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540518.6889721311</v>
+        <v>540546</v>
       </c>
       <c r="R17" t="n">
-        <v>7226522.217044306</v>
+        <v>7226526</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2433,19 +2198,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2472,15 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>67152929</v>
+        <v>67152906</v>
       </c>
       <c r="B18" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2488,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2512,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540513.9076692138</v>
+        <v>539907</v>
       </c>
       <c r="R18" t="n">
-        <v>7226533.088034357</v>
+        <v>7226649</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2545,19 +2295,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2584,37 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>67152998</v>
+        <v>67152915</v>
       </c>
       <c r="B19" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2624,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540518.2679172017</v>
+        <v>540025</v>
       </c>
       <c r="R19" t="n">
-        <v>7226522.21127918</v>
+        <v>7226497</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2657,19 +2392,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2696,37 +2421,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>67152986</v>
+        <v>67152917</v>
       </c>
       <c r="B20" t="n">
-        <v>93056</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2813</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2736,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540117.7882163015</v>
+        <v>540031</v>
       </c>
       <c r="R20" t="n">
-        <v>7226489.834392915</v>
+        <v>7226608</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2769,19 +2489,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2808,15 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>67153016</v>
+        <v>67199594</v>
       </c>
       <c r="B21" t="n">
-        <v>94440</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2824,21 +2529,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1841</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2848,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540537.5447663796</v>
+        <v>540180</v>
       </c>
       <c r="R21" t="n">
-        <v>7226559.911437498</v>
+        <v>7226487</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2881,19 +2586,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2920,15 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>67153003</v>
+        <v>67199595</v>
       </c>
       <c r="B22" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2936,39 +2626,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Västansjön S sidan, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540550.7698249086</v>
+        <v>540020</v>
       </c>
       <c r="R22" t="n">
-        <v>7226516.767597744</v>
+        <v>7226541</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2998,19 +2683,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3037,15 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>67153020</v>
+        <v>67199600</v>
       </c>
       <c r="B23" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3053,21 +2723,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3077,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540481.7867958262</v>
+        <v>540051</v>
       </c>
       <c r="R23" t="n">
-        <v>7226541.481711788</v>
+        <v>7226523</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3110,19 +2780,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3149,50 +2809,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>67152958</v>
+        <v>67904798</v>
       </c>
       <c r="B24" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2809</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Västansjön S sidan, Ås lm</t>
+          <t>Västansjön, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540013.0242854129</v>
+        <v>539870</v>
       </c>
       <c r="R24" t="n">
-        <v>7226513.654078341</v>
+        <v>7226609</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3219,22 +2874,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3254,22 +2899,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
+          <t>Isak Vahlström, Elias Forsberg, Billy Lindblom</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>67152917</v>
+        <v>67904799</v>
       </c>
       <c r="B25" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3297,14 +2937,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Västansjön S sidan, Ås lm</t>
+          <t>Västansjön, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540031.1184944947</v>
+        <v>540310</v>
       </c>
       <c r="R25" t="n">
-        <v>7226608.119012741</v>
+        <v>7226390</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3331,22 +2971,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3366,22 +2996,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
+          <t>Isak Vahlström, Elias Forsberg, Billy Lindblom</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>67152977</v>
+        <v>67904800</v>
       </c>
       <c r="B26" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3389,34 +3014,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Västansjön S sidan, Ås lm</t>
+          <t>Västansjön, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540574.942988319</v>
+        <v>540334</v>
       </c>
       <c r="R26" t="n">
-        <v>7226504.479877667</v>
+        <v>7226354</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3443,22 +3068,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3478,22 +3093,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
+          <t>Isak Vahlström, Elias Forsberg, Billy Lindblom</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>67152886</v>
+        <v>67153012</v>
       </c>
       <c r="B27" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3501,21 +3111,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3525,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540017.9177164265</v>
+        <v>540575</v>
       </c>
       <c r="R27" t="n">
-        <v>7226525.497938277</v>
+        <v>7226506</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3558,19 +3168,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3597,15 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>67152873</v>
+        <v>67153013</v>
       </c>
       <c r="B28" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3613,21 +3208,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3637,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540469.5820338896</v>
+        <v>539969</v>
       </c>
       <c r="R28" t="n">
-        <v>7226540.894147455</v>
+        <v>7226614</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3670,19 +3265,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3709,15 +3294,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>67153024</v>
+        <v>67904522</v>
       </c>
       <c r="B29" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3725,34 +3305,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Västansjön S sidan, Ås lm</t>
+          <t>Västansjön, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540026.2533566291</v>
+        <v>539871</v>
       </c>
       <c r="R29" t="n">
-        <v>7226500.793340409</v>
+        <v>7226610</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3779,22 +3359,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3814,22 +3384,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
+          <t>Isak Vahlström, Elias Forsberg, Billy Lindblom</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>67152905</v>
+        <v>67904524</v>
       </c>
       <c r="B30" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3837,34 +3402,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Västansjön S sidan, Ås lm</t>
+          <t>Västansjön, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540546.0056814061</v>
+        <v>540386</v>
       </c>
       <c r="R30" t="n">
-        <v>7226526.376895838</v>
+        <v>7226308</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3891,22 +3456,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3926,22 +3481,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
+          <t>Isak Vahlström, Elias Forsberg, Billy Lindblom</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>67152989</v>
+        <v>67152872</v>
       </c>
       <c r="B31" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3949,21 +3499,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3973,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540513.5269188571</v>
+        <v>540512</v>
       </c>
       <c r="R31" t="n">
-        <v>7226530.138396097</v>
+        <v>7226532</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4006,19 +3556,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4045,15 +3585,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>67153005</v>
+        <v>67152873</v>
       </c>
       <c r="B32" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4061,39 +3596,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Västansjön S sidan, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540205.6217139622</v>
+        <v>540470</v>
       </c>
       <c r="R32" t="n">
-        <v>7226441.390872641</v>
+        <v>7226541</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4123,19 +3653,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4162,15 +3682,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>67152915</v>
+        <v>67152874</v>
       </c>
       <c r="B33" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4178,21 +3693,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4202,10 +3717,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540025.4681230678</v>
+        <v>540185</v>
       </c>
       <c r="R33" t="n">
-        <v>7226496.576371669</v>
+        <v>7226436</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4235,19 +3750,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4274,15 +3779,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>67152880</v>
+        <v>67152875</v>
       </c>
       <c r="B34" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4314,10 +3814,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540163.2340856222</v>
+        <v>540174</v>
       </c>
       <c r="R34" t="n">
-        <v>7226492.554011864</v>
+        <v>7226442</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4347,19 +3847,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4386,37 +3876,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>67152941</v>
+        <v>67152879</v>
       </c>
       <c r="B35" t="n">
-        <v>92688</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2387</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4426,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540150.3479045916</v>
+        <v>540321</v>
       </c>
       <c r="R35" t="n">
-        <v>7226449.053302137</v>
+        <v>7226424</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4459,19 +3944,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4498,37 +3973,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>67152942</v>
+        <v>67152880</v>
       </c>
       <c r="B36" t="n">
-        <v>92688</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2387</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4538,10 +4008,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540144.3377756979</v>
+        <v>540163</v>
       </c>
       <c r="R36" t="n">
-        <v>7226488.51188516</v>
+        <v>7226493</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4571,19 +4041,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4610,15 +4070,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>67152979</v>
+        <v>67152881</v>
       </c>
       <c r="B37" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4626,21 +4081,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4650,10 +4105,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>539967.8882708425</v>
+        <v>540088</v>
       </c>
       <c r="R37" t="n">
-        <v>7226612.732360988</v>
+        <v>7226492</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4683,19 +4138,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4725,12 +4170,7 @@
         <v>67152882</v>
       </c>
       <c r="B38" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4762,10 +4202,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540027.4312025963</v>
+        <v>540027</v>
       </c>
       <c r="R38" t="n">
-        <v>7226507.118782741</v>
+        <v>7226507</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4795,19 +4235,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4834,15 +4264,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>67152981</v>
+        <v>67199578</v>
       </c>
       <c r="B39" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4850,21 +4275,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1467</v>
+        <v>1312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4874,10 +4299,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540583.8659409567</v>
+        <v>539980</v>
       </c>
       <c r="R39" t="n">
-        <v>7226498.713319607</v>
+        <v>7226585</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4907,19 +4332,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4939,22 +4354,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
+          <t>Anton Gustafsson, Eino Kenttä, Johanna Eriksson, Ingemar Södergren, Linda Johannesson, Nils Ericson, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>67153013</v>
+        <v>67199579</v>
       </c>
       <c r="B40" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4962,21 +4372,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4986,10 +4396,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>539969.1343555669</v>
+        <v>540036</v>
       </c>
       <c r="R40" t="n">
-        <v>7226614.011046479</v>
+        <v>7226775</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5019,19 +4429,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5051,22 +4451,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
+          <t>Anton Gustafsson, Eino Kenttä, Johanna Eriksson, Ingemar Södergren, Linda Johannesson, Nils Ericson, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>67152875</v>
+        <v>67199580</v>
       </c>
       <c r="B41" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5098,10 +4493,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540174.0303211516</v>
+        <v>540087</v>
       </c>
       <c r="R41" t="n">
-        <v>7226441.803129945</v>
+        <v>7226499</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5131,19 +4526,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5163,44 +4548,39 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
+          <t>Anton Gustafsson, Eino Kenttä, Johanna Eriksson, Ingemar Södergren, Linda Johannesson, Nils Ericson, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>67152957</v>
+        <v>67199581</v>
       </c>
       <c r="B42" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2809</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5210,10 +4590,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540137.2539159526</v>
+        <v>540575</v>
       </c>
       <c r="R42" t="n">
-        <v>7226482.947515048</v>
+        <v>7226556</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5243,19 +4623,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5275,22 +4645,17 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
+          <t>Anton Gustafsson, Eino Kenttä, Johanna Eriksson, Ingemar Södergren, Linda Johannesson, Nils Ericson, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>67152888</v>
+        <v>67152981</v>
       </c>
       <c r="B43" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5298,21 +4663,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5322,10 +4687,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540522.9174502905</v>
+        <v>540584</v>
       </c>
       <c r="R43" t="n">
-        <v>7226551.719149516</v>
+        <v>7226499</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5355,19 +4720,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5387,44 +4742,39 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
+          <t>Anton Gustafsson, Eino Kenttä, Johanna Eriksson, Ingemar Södergren, Linda Johannesson, Nils Ericson, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>67152869</v>
+        <v>67199644</v>
       </c>
       <c r="B44" t="n">
-        <v>73680</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92097</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>306</v>
+        <v>1588</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5434,10 +4784,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540102.3065755182</v>
+        <v>540038</v>
       </c>
       <c r="R44" t="n">
-        <v>7226451.346395567</v>
+        <v>7226755</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5467,19 +4817,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5506,15 +4846,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>67153017</v>
+        <v>67153016</v>
       </c>
       <c r="B45" t="n">
-        <v>94440</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97453</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5546,10 +4881,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540025.7187763485</v>
+        <v>540538</v>
       </c>
       <c r="R45" t="n">
-        <v>7226571.451865776</v>
+        <v>7226560</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5579,19 +4914,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5618,15 +4943,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>67153006</v>
+        <v>67153017</v>
       </c>
       <c r="B46" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97453</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5634,39 +4954,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>1841</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Västansjön S sidan, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540077.0878424841</v>
+        <v>540026</v>
       </c>
       <c r="R46" t="n">
-        <v>7226478.766989839</v>
+        <v>7226571</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5696,19 +5011,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5735,15 +5040,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>67152930</v>
+        <v>67199643</v>
       </c>
       <c r="B47" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97453</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5751,21 +5051,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>864</v>
+        <v>1841</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5775,10 +5075,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540470.8451906398</v>
+        <v>540513</v>
       </c>
       <c r="R47" t="n">
-        <v>7226540.911422254</v>
+        <v>7226560</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5808,19 +5108,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5847,15 +5137,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>67199594</v>
+        <v>67152989</v>
       </c>
       <c r="B48" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5863,21 +5148,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5887,10 +5172,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540180.1506774763</v>
+        <v>540514</v>
       </c>
       <c r="R48" t="n">
-        <v>7226487.315373464</v>
+        <v>7226530</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5920,19 +5205,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5952,44 +5227,39 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
+          <t>Anton Gustafsson, Eino Kenttä, Johanna Eriksson, Ingemar Södergren, Linda Johannesson, Nils Ericson, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>67199616</v>
+        <v>67152990</v>
       </c>
       <c r="B49" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5999,10 +5269,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540567.3756780688</v>
+        <v>540111</v>
       </c>
       <c r="R49" t="n">
-        <v>7226534.241159596</v>
+        <v>7226459</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6032,19 +5302,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6064,22 +5324,17 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
+          <t>Anton Gustafsson, Eino Kenttä, Johanna Eriksson, Ingemar Södergren, Linda Johannesson, Nils Ericson, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>67199600</v>
+        <v>67199625</v>
       </c>
       <c r="B50" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6087,21 +5342,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6111,10 +5366,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>540050.7997889903</v>
+        <v>540281</v>
       </c>
       <c r="R50" t="n">
-        <v>7226522.998365539</v>
+        <v>7226444</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6144,21 +5399,11 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6167,6 +5412,21 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6183,15 +5443,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>67199643</v>
+        <v>67199626</v>
       </c>
       <c r="B51" t="n">
-        <v>94440</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6199,21 +5454,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1841</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6223,10 +5478,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>540513.1181325018</v>
+        <v>540578</v>
       </c>
       <c r="R51" t="n">
-        <v>7226559.997552103</v>
+        <v>7226546</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6256,19 +5511,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6295,15 +5540,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>67199650</v>
+        <v>67199627</v>
       </c>
       <c r="B52" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6311,21 +5551,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6335,10 +5575,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>540026.2193464336</v>
+        <v>540131</v>
       </c>
       <c r="R52" t="n">
-        <v>7226534.443450293</v>
+        <v>7226492</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6368,21 +5608,11 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6391,6 +5621,21 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6407,15 +5652,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>67199649</v>
+        <v>67199629</v>
       </c>
       <c r="B53" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6423,21 +5663,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6447,10 +5687,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540043.0956096348</v>
+        <v>540542</v>
       </c>
       <c r="R53" t="n">
-        <v>7226532.147984094</v>
+        <v>7226569</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6480,19 +5720,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6519,15 +5749,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>67199625</v>
+        <v>67199630</v>
       </c>
       <c r="B54" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6559,10 +5784,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540280.9753977641</v>
+        <v>540393</v>
       </c>
       <c r="R54" t="n">
-        <v>7226443.677513453</v>
+        <v>7226429</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6592,21 +5817,11 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6615,21 +5830,6 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6646,37 +5846,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>67199627</v>
+        <v>67152941</v>
       </c>
       <c r="B55" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95962</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>2387</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6686,10 +5881,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540131.2393028793</v>
+        <v>540150</v>
       </c>
       <c r="R55" t="n">
-        <v>7226491.699318884</v>
+        <v>7226449</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6719,21 +5914,11 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6742,21 +5927,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6773,37 +5943,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>67199588</v>
+        <v>67152942</v>
       </c>
       <c r="B56" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95962</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>2387</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6813,10 +5978,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540523.6270939959</v>
+        <v>540144</v>
       </c>
       <c r="R56" t="n">
-        <v>7226561.403328117</v>
+        <v>7226489</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6846,19 +6011,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6885,37 +6040,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>67199586</v>
+        <v>67199612</v>
       </c>
       <c r="B57" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95962</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>2387</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6925,10 +6075,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540578.473074158</v>
+        <v>540176</v>
       </c>
       <c r="R57" t="n">
-        <v>7226554.162954518</v>
+        <v>7226498</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6958,19 +6108,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6997,37 +6137,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>67199578</v>
+        <v>67152956</v>
       </c>
       <c r="B58" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1312</v>
+        <v>2809</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7037,10 +6172,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>539979.6313922224</v>
+        <v>539891</v>
       </c>
       <c r="R58" t="n">
-        <v>7226585.130047672</v>
+        <v>7226662</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7070,19 +6205,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7109,37 +6234,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>67199636</v>
+        <v>67152957</v>
       </c>
       <c r="B59" t="n">
-        <v>90160</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>918</v>
+        <v>2809</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7149,10 +6269,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540041.6841159589</v>
+        <v>540137</v>
       </c>
       <c r="R59" t="n">
-        <v>7226729.818462139</v>
+        <v>7226483</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7182,19 +6302,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7221,15 +6331,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>67199612</v>
+        <v>67152958</v>
       </c>
       <c r="B60" t="n">
-        <v>92688</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7237,21 +6342,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2387</v>
+        <v>2809</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7261,10 +6366,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540175.7916309767</v>
+        <v>540013</v>
       </c>
       <c r="R60" t="n">
-        <v>7226498.192734895</v>
+        <v>7226514</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7294,19 +6399,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7333,15 +6428,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>67199634</v>
+        <v>67152986</v>
       </c>
       <c r="B61" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96350</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7349,21 +6439,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>2813</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7373,10 +6463,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>540087.3409089444</v>
+        <v>540118</v>
       </c>
       <c r="R61" t="n">
-        <v>7226499.096410993</v>
+        <v>7226490</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7406,19 +6496,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7438,44 +6518,39 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
+          <t>Anton Gustafsson, Eino Kenttä, Johanna Eriksson, Ingemar Södergren, Linda Johannesson, Nils Ericson, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>67199581</v>
+        <v>67152886</v>
       </c>
       <c r="B62" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7485,10 +6560,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>540575.0816055206</v>
+        <v>540018</v>
       </c>
       <c r="R62" t="n">
-        <v>7226555.79896749</v>
+        <v>7226525</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7518,19 +6593,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7557,37 +6622,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>67199587</v>
+        <v>67199585</v>
       </c>
       <c r="B63" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7597,10 +6657,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540565.777728403</v>
+        <v>540164</v>
       </c>
       <c r="R63" t="n">
-        <v>7226497.203400305</v>
+        <v>7226499</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7630,19 +6690,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7662,44 +6712,39 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
+          <t>Anton Gustafsson, Eino Kenttä, Johanna Eriksson, Ingemar Södergren, Linda Johannesson, Nils Ericson, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>67199595</v>
+        <v>67199586</v>
       </c>
       <c r="B64" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7709,10 +6754,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540019.8125528444</v>
+        <v>540578</v>
       </c>
       <c r="R64" t="n">
-        <v>7226541.086868004</v>
+        <v>7226554</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7742,19 +6787,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7774,22 +6809,17 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
+          <t>Anton Gustafsson, Eino Kenttä, Johanna Eriksson, Ingemar Södergren, Linda Johannesson, Nils Ericson, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>67199580</v>
+        <v>67153020</v>
       </c>
       <c r="B65" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7797,21 +6827,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7821,10 +6851,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540087.3409089444</v>
+        <v>540482</v>
       </c>
       <c r="R65" t="n">
-        <v>7226499.096410993</v>
+        <v>7226541</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7854,19 +6884,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7893,37 +6913,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>67199576</v>
+        <v>67153021</v>
       </c>
       <c r="B66" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7933,10 +6948,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540566.95462483</v>
+        <v>540174</v>
       </c>
       <c r="R66" t="n">
-        <v>7226534.235387539</v>
+        <v>7226442</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7966,19 +6981,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8005,15 +7010,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>67199645</v>
+        <v>67153022</v>
       </c>
       <c r="B67" t="n">
-        <v>76504</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8021,21 +7021,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>314</v>
+        <v>6440</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8045,10 +7045,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540087.3409089444</v>
+        <v>540164</v>
       </c>
       <c r="R67" t="n">
-        <v>7226499.096410993</v>
+        <v>7226492</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8078,19 +7078,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8117,15 +7107,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>67199626</v>
+        <v>67153024</v>
       </c>
       <c r="B68" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8133,21 +7118,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8157,10 +7142,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540578.1615922537</v>
+        <v>540026</v>
       </c>
       <c r="R68" t="n">
-        <v>7226546.166715712</v>
+        <v>7226501</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8190,19 +7175,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8229,15 +7204,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>67199585</v>
+        <v>67199649</v>
       </c>
       <c r="B69" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8245,21 +7215,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8269,10 +7239,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540163.9905852181</v>
+        <v>540043</v>
       </c>
       <c r="R69" t="n">
-        <v>7226498.873816311</v>
+        <v>7226532</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8302,19 +7272,9 @@
           <t>2017-08-08</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2017-08-08</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8341,15 +7301,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>67904770</v>
+        <v>67199650</v>
       </c>
       <c r="B70" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8357,34 +7312,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>864</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Västansjön, Ås lm</t>
+          <t>Västansjön S sidan, Ås lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540392.8539792624</v>
+        <v>540026</v>
       </c>
       <c r="R70" t="n">
-        <v>7226300.076740963</v>
+        <v>7226534</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8411,22 +7366,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2017-10-08</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-08</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2017-10-08</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-08</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8446,22 +7391,17 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Elias Forsberg, Billy Lindblom</t>
+          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>67904799</v>
+        <v>67904510</v>
       </c>
       <c r="B71" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8469,21 +7409,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8493,10 +7433,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540310.3468742417</v>
+        <v>539828</v>
       </c>
       <c r="R71" t="n">
-        <v>7226389.813905211</v>
+        <v>7226629</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8526,19 +7466,9 @@
           <t>2017-10-08</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2017-10-08</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8565,50 +7495,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>67904800</v>
+        <v>67152998</v>
       </c>
       <c r="B72" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Västansjön, Ås lm</t>
+          <t>Västansjön S sidan, Ås lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540333.5835275737</v>
+        <v>540518</v>
       </c>
       <c r="R72" t="n">
-        <v>7226353.53359694</v>
+        <v>7226522</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8635,22 +7560,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2017-10-08</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-08</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2017-10-08</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-08</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8670,57 +7585,52 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Elias Forsberg, Billy Lindblom</t>
+          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>67904524</v>
+        <v>67152999</v>
       </c>
       <c r="B73" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Västansjön, Ås lm</t>
+          <t>Västansjön S sidan, Ås lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540386.0018081079</v>
+        <v>540109</v>
       </c>
       <c r="R73" t="n">
-        <v>7226308.396505922</v>
+        <v>7226451</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8747,22 +7657,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2017-10-08</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-08</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2017-10-08</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-08</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8782,10 +7682,1199 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Elias Forsberg, Billy Lindblom</t>
+          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>67199633</v>
+      </c>
+      <c r="B74" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Västansjön S sidan, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>540542</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7226569</v>
+      </c>
+      <c r="S74" t="n">
+        <v>25</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2017-08-08</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2017-08-08</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>67199634</v>
+      </c>
+      <c r="B75" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Västansjön S sidan, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>540087</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7226499</v>
+      </c>
+      <c r="S75" t="n">
+        <v>25</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2017-08-08</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2017-08-08</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson, Isak Vahlström, Nils Ericson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>67199635</v>
+      </c>
+      <c r="B76" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Västansjön S sidan, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>540392</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7226430</v>
+      </c>
+      <c r="S76" t="n">
+        <v>25</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2017-08-08</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2017-08-08</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>67152866</v>
+      </c>
+      <c r="B77" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Västansjön S sidan, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>540519</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7226522</v>
+      </c>
+      <c r="S77" t="n">
+        <v>25</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2017-08-08</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2017-08-08</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>67199576</v>
+      </c>
+      <c r="B78" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Västansjön S sidan, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>540567</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7226534</v>
+      </c>
+      <c r="S78" t="n">
+        <v>25</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2017-08-08</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2017-08-08</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Anton Gustafsson, Eino Kenttä, Johanna Eriksson, Ingemar Södergren, Linda Johannesson, Nils Ericson, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>67199616</v>
+      </c>
+      <c r="B79" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Västansjön S sidan, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>540567</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7226534</v>
+      </c>
+      <c r="S79" t="n">
+        <v>25</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2017-08-08</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2017-08-08</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>67153003</v>
+      </c>
+      <c r="B80" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Västansjön S sidan, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>540551</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7226517</v>
+      </c>
+      <c r="S80" t="n">
+        <v>25</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2017-08-08</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2017-08-08</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>67153005</v>
+      </c>
+      <c r="B81" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Västansjön S sidan, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>540206</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7226441</v>
+      </c>
+      <c r="S81" t="n">
+        <v>25</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2017-08-08</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2017-08-08</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>67153006</v>
+      </c>
+      <c r="B82" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Västansjön S sidan, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>540077</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7226479</v>
+      </c>
+      <c r="S82" t="n">
+        <v>25</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2017-08-08</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2017-08-08</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>67153007</v>
+      </c>
+      <c r="B83" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Västansjön S sidan, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>540028</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7226510</v>
+      </c>
+      <c r="S83" t="n">
+        <v>25</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2017-08-08</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2017-08-08</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>67199638</v>
+      </c>
+      <c r="B84" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Västansjön S sidan, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>540049</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7226772</v>
+      </c>
+      <c r="S84" t="n">
+        <v>25</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2017-08-08</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2017-08-08</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Nils Ericson, Linda Johannesson, Ingemar Södergren, Johanna Eriksson, Eino Kenttä, Anton Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>67199575</v>
+      </c>
+      <c r="B85" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Västansjön S sidan, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>540394</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7226451</v>
+      </c>
+      <c r="S85" t="n">
+        <v>25</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2017-08-08</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2017-08-08</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Anton Gustafsson, Eino Kenttä, Johanna Eriksson, Ingemar Södergren, Linda Johannesson, Nils Ericson, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
